--- a/artfynd/A 27766-2026 artfynd.xlsx
+++ b/artfynd/A 27766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042884</v>
       </c>
       <c r="B2" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042885</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27766-2026 artfynd.xlsx
+++ b/artfynd/A 27766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042884</v>
       </c>
       <c r="B2" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042885</v>
       </c>
       <c r="B3" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
